--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER_KeyBERT_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER_KeyBERT_CS.xlsx
@@ -483,11 +483,11 @@
         <v>0.2254</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2051</v>
+        <v>0.2329</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.2102</v>
+        <v>0.2297</v>
       </c>
     </row>
     <row r="3">
@@ -502,10 +502,10 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.2346</v>
+        <v>0.3383</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2041</v>
+        <v>0.3292</v>
       </c>
     </row>
     <row r="4">
@@ -520,13 +520,13 @@
         <v>0.3234</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2099</v>
+        <v>0.2816</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2325</v>
+        <v>0.3188</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2706</v>
+        <v>0.3955</v>
       </c>
       <c r="H4" t="n">
         <v>0.2082</v>
@@ -543,13 +543,13 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.3577</v>
+        <v>0.4183</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2662</v>
+        <v>0.5218</v>
       </c>
       <c r="H5" t="n">
-        <v>0.202</v>
+        <v>0.3472</v>
       </c>
     </row>
     <row r="6">
@@ -562,13 +562,13 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.2954</v>
+        <v>0.3623</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2495</v>
+        <v>0.3283</v>
       </c>
       <c r="G6" t="n">
-        <v>0.247</v>
+        <v>0.2681</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -586,10 +586,10 @@
         <v>0.2021</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2123</v>
+        <v>0.2359</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2071</v>
+        <v>0.2328</v>
       </c>
     </row>
     <row r="8">
@@ -602,13 +602,13 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>0.2431</v>
+        <v>0.3272</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2053</v>
+        <v>0.2497</v>
       </c>
       <c r="G8" t="n">
-        <v>0.229</v>
+        <v>0.3082</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -638,7 +638,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>0.2106</v>
+        <v>0.2333</v>
       </c>
       <c r="F10" t="n">
         <v>0.2287</v>
@@ -658,13 +658,13 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.2142</v>
+        <v>0.2908</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2293</v>
+        <v>0.3114</v>
       </c>
       <c r="G11" t="n">
-        <v>0.211</v>
+        <v>0.3672</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -730,19 +730,19 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0.2336</v>
+        <v>0.4272</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2071</v>
+        <v>0.3256</v>
       </c>
       <c r="E15" t="n">
         <v>0.4343</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2323</v>
+        <v>0.4065</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2158</v>
+        <v>0.3121</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>0.2</v>
+        <v>0.2333</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
@@ -776,7 +776,7 @@
         <v>0.2364</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2103</v>
+        <v>0.2163</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -797,7 +797,7 @@
         <v>0.2182</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3595</v>
+        <v>0.3613</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -810,22 +810,22 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.2226</v>
+        <v>0.4039</v>
       </c>
       <c r="D19" t="n">
         <v>0.2617</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2204</v>
+        <v>0.2819</v>
       </c>
       <c r="F19" t="n">
         <v>0.4033</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2222</v>
+        <v>0.2464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2639</v>
+        <v>0.3383</v>
       </c>
     </row>
     <row r="20">
@@ -836,19 +836,19 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.2369</v>
+        <v>0.3276</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2037</v>
+        <v>0.3292</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>0.2314</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2141</v>
+        <v>0.3476</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2402</v>
+        <v>0.2932</v>
       </c>
       <c r="H20" t="n">
         <v>0.2456</v>
@@ -864,13 +864,13 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.2022</v>
+        <v>0.3023</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2005</v>
+        <v>0.2583</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2348</v>
+        <v>0.3626</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -920,10 +920,10 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.2307</v>
+        <v>0.4238</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2161</v>
+        <v>0.3433</v>
       </c>
     </row>
     <row r="25">
@@ -934,22 +934,22 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.2934</v>
+        <v>0.4808</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2543</v>
+        <v>0.3685</v>
       </c>
       <c r="E25" t="n">
-        <v>0.239</v>
+        <v>0.3658</v>
       </c>
       <c r="F25" t="n">
-        <v>0.203</v>
+        <v>0.3691</v>
       </c>
       <c r="G25" t="n">
-        <v>0.247</v>
+        <v>0.3579</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2363</v>
+        <v>0.3425</v>
       </c>
     </row>
     <row r="26">
@@ -961,7 +961,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>0.2043</v>
+        <v>0.2321</v>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
@@ -980,14 +980,14 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0.2316</v>
+        <v>0.2577</v>
       </c>
       <c r="D27" t="n">
         <v>0.2322</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>0.2347</v>
+        <v>0.2758</v>
       </c>
       <c r="G27" t="n">
         <v>0.2743</v>
@@ -1011,11 +1011,11 @@
         <v>0.2451</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2094</v>
+        <v>0.2133</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.2179</v>
+        <v>0.2521</v>
       </c>
     </row>
     <row r="29">
@@ -1026,19 +1026,19 @@
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.2566</v>
+        <v>0.2892</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2022</v>
+        <v>0.2781</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2038</v>
+        <v>0.34</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2197</v>
+        <v>0.3389</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2004</v>
+        <v>0.293</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1052,12 +1052,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>0.2504</v>
+        <v>0.2912</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.2249</v>
+        <v>0.2449</v>
       </c>
     </row>
     <row r="31">
@@ -1074,7 +1074,7 @@
         <v>0.3458</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2013</v>
+        <v>0.2242</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.216</v>
+        <v>0.2943</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -1130,10 +1130,10 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.226</v>
+        <v>0.3657</v>
       </c>
       <c r="H34" t="n">
-        <v>0.231</v>
+        <v>0.3389</v>
       </c>
     </row>
     <row r="35">
@@ -1146,16 +1146,16 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.2033</v>
+        <v>0.2923</v>
       </c>
       <c r="F35" t="n">
         <v>0.2298</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2018</v>
+        <v>0.3708</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2622</v>
+        <v>0.3495</v>
       </c>
     </row>
     <row r="36">
@@ -1166,19 +1166,19 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.209</v>
+        <v>0.31</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2119</v>
+        <v>0.3234</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2267</v>
+        <v>0.3234</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2116</v>
+        <v>0.3842</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2116</v>
+        <v>0.3644</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1194,7 +1194,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
-        <v>0.2093</v>
+        <v>0.226</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1228,7 +1228,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>0.2345</v>
+        <v>0.2753</v>
       </c>
       <c r="F39" t="n">
         <v>0.2749</v>
@@ -1244,13 +1244,13 @@
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.2338</v>
+        <v>0.3225</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
-        <v>0.2054</v>
+        <v>0.2272</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1268,10 +1268,10 @@
         <v>0.2379</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2093</v>
+        <v>0.2553</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2545</v>
+        <v>0.2594</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
         <v>0.3632</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2294</v>
+        <v>0.2349</v>
       </c>
       <c r="F42" t="n">
         <v>0.3133</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.4334</v>
+        <v>0.4457</v>
       </c>
       <c r="D43" t="n">
         <v>0.4268</v>
@@ -1320,10 +1320,10 @@
         <v>0.3658</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2477</v>
+        <v>0.396</v>
       </c>
       <c r="H43" t="n">
-        <v>0.244</v>
+        <v>0.4521</v>
       </c>
     </row>
     <row r="44">
@@ -1351,13 +1351,13 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>0.312</v>
+        <v>0.379</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2397</v>
+        <v>0.3746</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2173</v>
+        <v>0.3395</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.2066</v>
+        <v>0.2206</v>
       </c>
       <c r="D47" t="n">
         <v>0.2354</v>
@@ -1435,13 +1435,13 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>0.238</v>
+        <v>0.4499</v>
       </c>
       <c r="E49" t="n">
         <v>0.2236</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2116</v>
+        <v>0.2792</v>
       </c>
       <c r="G49" t="n">
         <v>0.2085</v>
@@ -1461,13 +1461,13 @@
         <v>0.2631</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2164</v>
+        <v>0.2407</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2016</v>
+        <v>0.2324</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2539</v>
+        <v>0.2955</v>
       </c>
     </row>
     <row r="51">
@@ -1480,7 +1480,7 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>0.2091</v>
+        <v>0.2138</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.2218</v>
+        <v>0.2814</v>
       </c>
       <c r="D52" t="n">
         <v>0.2216</v>
@@ -1510,7 +1510,7 @@
         <v>0.2286</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2041</v>
+        <v>0.2657</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -1522,19 +1522,19 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.2146</v>
+        <v>0.4395</v>
       </c>
       <c r="D53" t="n">
         <v>0.2321</v>
       </c>
       <c r="E53" t="n">
-        <v>0.23</v>
+        <v>0.2829</v>
       </c>
       <c r="F53" t="n">
         <v>0.2364</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2355</v>
+        <v>0.2394</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -1549,16 +1549,16 @@
         <v>0.3504</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2595</v>
+        <v>0.3001</v>
       </c>
       <c r="E54" t="n">
         <v>0.3771</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2181</v>
+        <v>0.4131</v>
       </c>
       <c r="G54" t="n">
-        <v>0.2354</v>
+        <v>0.2723</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1570,19 +1570,19 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.2535</v>
+        <v>0.2717</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2655</v>
+        <v>0.3782</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2587</v>
+        <v>0.2714</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2749</v>
+        <v>0.2916</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2015</v>
+        <v>0.3237</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1597,7 +1597,7 @@
         <v>0.3224</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2034</v>
+        <v>0.2697</v>
       </c>
       <c r="E56" t="n">
         <v>0.3431</v>
@@ -1618,19 +1618,19 @@
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="n">
-        <v>0.2435</v>
+        <v>0.3571</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2067</v>
+        <v>0.3522</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2098</v>
+        <v>0.3733</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2509</v>
+        <v>0.4018</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2902</v>
+        <v>0.3247</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1645,13 +1645,13 @@
         <v>0.3312</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2063</v>
+        <v>0.3058</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2538</v>
+        <v>0.3038</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2418</v>
+        <v>0.402</v>
       </c>
       <c r="G58" t="n">
         <v>0.2653</v>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2177</v>
+        <v>0.4399</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2155</v>
+        <v>0.2573</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2188</v>
+        <v>0.2384</v>
       </c>
       <c r="E59" t="n">
         <v>0.2074</v>
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2334</v>
+        <v>0.2809</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2634</v>
+        <v>0.5406</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2306</v>
+        <v>0.4117</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2097</v>
+        <v>0.5605</v>
       </c>
       <c r="F60" t="n">
         <v>0.2364</v>
@@ -1717,22 +1717,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2169</v>
+        <v>0.3199</v>
       </c>
       <c r="C61" t="n">
-        <v>0.202</v>
+        <v>0.3297</v>
       </c>
       <c r="D61" t="n">
         <v>0.2358</v>
       </c>
       <c r="E61" t="n">
-        <v>0.278</v>
+        <v>0.3191</v>
       </c>
       <c r="F61" t="n">
         <v>0.332</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2062</v>
+        <v>0.2394</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1744,13 +1744,13 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.2</v>
+        <v>0.2461</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2182</v>
+        <v>0.258</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2131</v>
+        <v>0.2622</v>
       </c>
       <c r="F62" t="n">
         <v>0.2146</v>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
-        <v>0.2015</v>
+        <v>0.2024</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0.2115</v>
+        <v>0.2888</v>
       </c>
       <c r="D64" t="n">
         <v>0.2658</v>
@@ -1845,7 +1845,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>0.2291</v>
+        <v>0.2572</v>
       </c>
       <c r="E67" t="n">
         <v>0.2337</v>
@@ -1864,19 +1864,19 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.2012</v>
+        <v>0.3875</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2181</v>
+        <v>0.3665</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2838</v>
+        <v>0.3623</v>
       </c>
       <c r="F68" t="n">
-        <v>0.221</v>
+        <v>0.2761</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2428</v>
+        <v>0.3506</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -1888,16 +1888,16 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.2347</v>
+        <v>0.3386</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2864</v>
+        <v>0.4132</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2169</v>
+        <v>0.3129</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2067</v>
+        <v>0.2983</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.206</v>
+        <v>0.413</v>
       </c>
       <c r="D70" t="n">
         <v>0.3964</v>
@@ -1932,13 +1932,13 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.2016</v>
+        <v>0.2909</v>
       </c>
       <c r="D71" t="n">
         <v>0.2114</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2019</v>
+        <v>0.2976</v>
       </c>
       <c r="F71" t="n">
         <v>0.2039</v>
@@ -1958,19 +1958,19 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0.2661</v>
+        <v>0.3967</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2051</v>
+        <v>0.3534</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2492</v>
+        <v>0.3535</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2083</v>
+        <v>0.3544</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2022</v>
+        <v>0.3442</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -1988,13 +1988,13 @@
         <v>0.2871</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2398</v>
+        <v>0.324</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2079</v>
+        <v>0.3924</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2038</v>
+        <v>0.3497</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2006,13 +2006,13 @@
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="n">
-        <v>0.2026</v>
+        <v>0.2594</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2804</v>
+        <v>0.2811</v>
       </c>
       <c r="E74" t="n">
-        <v>0.2518</v>
+        <v>0.4031</v>
       </c>
       <c r="F74" t="n">
         <v>0.2763</v>
@@ -2028,19 +2028,19 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.3072</v>
+        <v>0.3688</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2003</v>
+        <v>0.5265</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3127</v>
+        <v>0.396</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2694</v>
+        <v>0.3208</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2105</v>
+        <v>0.3036</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2052,13 +2052,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0.2491</v>
+        <v>0.3594</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2644</v>
+        <v>0.3696</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2805</v>
+        <v>0.3929</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.2454</v>
+        <v>0.2728</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2312</v>
+        <v>0.3338</v>
       </c>
       <c r="E77" t="n">
         <v>0.2418</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0.2115</v>
+        <v>0.3494</v>
       </c>
       <c r="D78" t="n">
         <v>0.327</v>
@@ -2103,7 +2103,7 @@
         <v>0.2983</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2005</v>
+        <v>0.3509</v>
       </c>
       <c r="G78" t="n">
         <v>0.213</v>
@@ -2121,16 +2121,16 @@
         <v>0.3195</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2017</v>
+        <v>0.318</v>
       </c>
       <c r="E79" t="n">
         <v>0.285</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2414</v>
+        <v>0.3385</v>
       </c>
       <c r="G79" t="n">
-        <v>0.3103</v>
+        <v>0.3847</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2142,16 +2142,16 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.2486</v>
+        <v>0.5181</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2875</v>
+        <v>0.5992</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2443</v>
+        <v>0.5092</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2788</v>
+        <v>0.581</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -2164,19 +2164,19 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2109</v>
+        <v>0.4395</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2007</v>
+        <v>0.4182</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2129</v>
+        <v>0.4436</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2783</v>
+        <v>0.58</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2326</v>
+        <v>0.4847</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2191,16 +2191,16 @@
         <v>0.3351</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2343</v>
+        <v>0.4882</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2136</v>
+        <v>0.4452</v>
       </c>
       <c r="F82" t="n">
         <v>0.3077</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2469</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2265,7 +2265,7 @@
         <v>0.3227</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2151</v>
+        <v>0.3653</v>
       </c>
       <c r="G85" t="n">
         <v>0.3286</v>
@@ -2281,19 +2281,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2018</v>
+        <v>0.4967</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2137</v>
+        <v>0.244</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2008</v>
+        <v>0.3225</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2371</v>
+        <v>0.4724</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2618</v>
+        <v>0.3224</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2342,12 +2342,12 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>0.2084</v>
+        <v>0.2372</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>0.2131</v>
+        <v>0.247</v>
       </c>
     </row>
     <row r="90">
@@ -2361,10 +2361,10 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.2104</v>
+        <v>0.4313</v>
       </c>
       <c r="G90" t="n">
-        <v>0.2019</v>
+        <v>0.3385</v>
       </c>
       <c r="H90" t="n">
         <v>0.2412</v>
@@ -2387,7 +2387,7 @@
         <v>0.2909</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2385</v>
+        <v>0.4604</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -2399,19 +2399,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2591</v>
+        <v>0.3019</v>
       </c>
       <c r="C92" t="n">
         <v>0.2937</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2547</v>
+        <v>0.2736</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2451</v>
+        <v>0.3671</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2915</v>
+        <v>0.3391</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -2424,16 +2424,16 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.2433</v>
+        <v>0.2623</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2045</v>
+        <v>0.2159</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2066</v>
+        <v>0.2606</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2214</v>
+        <v>0.2391</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2302</v>
+        <v>0.3603</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2434</v>
+        <v>0.3086</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2337</v>
+        <v>0.3061</v>
       </c>
       <c r="E94" t="n">
-        <v>0.208</v>
+        <v>0.2885</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2679</v>
+        <v>0.2938</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -2475,13 +2475,13 @@
         <v>0.4654</v>
       </c>
       <c r="D95" t="n">
-        <v>0.2001</v>
+        <v>0.2378</v>
       </c>
       <c r="E95" t="n">
         <v>0.4871</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2182</v>
+        <v>0.3288</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
@@ -2519,7 +2519,7 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>0.2368</v>
+        <v>0.2668</v>
       </c>
       <c r="E97" t="n">
         <v>0.2082</v>
@@ -2554,19 +2554,19 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.327</v>
+        <v>0.4064</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4</v>
+        <v>0.4158</v>
       </c>
       <c r="E99" t="n">
-        <v>0.3541</v>
+        <v>0.3925</v>
       </c>
       <c r="F99" t="n">
         <v>0.4072</v>
       </c>
       <c r="G99" t="n">
-        <v>0.3253</v>
+        <v>0.4445</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2578,16 +2578,16 @@
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="n">
-        <v>0.2345</v>
+        <v>0.497</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2302</v>
+        <v>0.6554</v>
       </c>
       <c r="E100" t="n">
         <v>0.3308</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2076</v>
+        <v>0.2179</v>
       </c>
       <c r="G100" t="n">
         <v>0.3829</v>
@@ -2602,22 +2602,22 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.2238</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2733</v>
+        <v>0.4549</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2021</v>
+        <v>0.4435</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2366</v>
+        <v>0.2844</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2206</v>
+        <v>0.3034</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2687</v>
+        <v>0.4069</v>
       </c>
     </row>
     <row r="102">
@@ -2671,7 +2671,7 @@
         <v>0.3937</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2028</v>
+        <v>0.217</v>
       </c>
       <c r="G104" t="n">
         <v>0.276</v>
@@ -2692,10 +2692,10 @@
         <v>0.2545</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2686</v>
+        <v>0.3255</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2609</v>
+        <v>0.3383</v>
       </c>
       <c r="G105" t="n">
         <v>0.3579</v>
@@ -2709,15 +2709,15 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.2255</v>
+        <v>0.2373</v>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>0.2281</v>
+        <v>0.2415</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2564</v>
+        <v>0.2736</v>
       </c>
       <c r="G106" t="n">
         <v>0.2091</v>
@@ -2735,13 +2735,13 @@
         <v>0.3664</v>
       </c>
       <c r="D107" t="n">
-        <v>0.2428</v>
+        <v>0.2814</v>
       </c>
       <c r="E107" t="n">
         <v>0.4983</v>
       </c>
       <c r="F107" t="n">
-        <v>0.2356</v>
+        <v>0.3347</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="n">
-        <v>0.3056</v>
+        <v>0.3342</v>
       </c>
       <c r="D108" t="n">
-        <v>0.3056</v>
+        <v>0.3342</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2237</v>
+        <v>0.2321</v>
       </c>
       <c r="F108" t="n">
         <v>0.2696</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2607</v>
+        <v>0.3508</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -2788,7 +2788,7 @@
         <v>0.2009</v>
       </c>
       <c r="G109" t="n">
-        <v>0.2025</v>
+        <v>0.2148</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -2804,7 +2804,7 @@
         <v>0.3339</v>
       </c>
       <c r="E110" t="n">
-        <v>0.2469</v>
+        <v>0.4001</v>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
@@ -2829,7 +2829,7 @@
         <v>0.2033</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2615</v>
+        <v>0.3064</v>
       </c>
       <c r="G111" t="n">
         <v>0.2165</v>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.2247</v>
+        <v>0.3129</v>
       </c>
       <c r="C112" t="n">
         <v>0.3342</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3203</v>
+        <v>0.446</v>
       </c>
       <c r="E112" t="n">
         <v>0.3675</v>
@@ -2858,7 +2858,7 @@
         <v>0.2241</v>
       </c>
       <c r="G112" t="n">
-        <v>0.2368</v>
+        <v>0.3296</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -2879,7 +2879,7 @@
         <v>0.3535</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2688</v>
+        <v>0.2809</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
@@ -2924,19 +2924,19 @@
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
-        <v>0.2529</v>
+        <v>0.3217</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2969</v>
+        <v>0.3672</v>
       </c>
       <c r="E116" t="n">
-        <v>0.213</v>
+        <v>0.2316</v>
       </c>
       <c r="F116" t="n">
         <v>0.2048</v>
       </c>
       <c r="G116" t="n">
-        <v>0.206</v>
+        <v>0.2145</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -2951,14 +2951,14 @@
         <v>0.2073</v>
       </c>
       <c r="D117" t="n">
-        <v>0.2198</v>
+        <v>0.3047</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2692</v>
+        <v>0.3165</v>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>0.2222</v>
+        <v>0.2455</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -2979,7 +2979,7 @@
         <v>0.4062</v>
       </c>
       <c r="F118" t="n">
-        <v>0.2605</v>
+        <v>0.4889</v>
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
@@ -2992,16 +2992,16 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>0.2207</v>
+        <v>0.2666</v>
       </c>
       <c r="D119" t="n">
-        <v>0.2113</v>
+        <v>0.2997</v>
       </c>
       <c r="E119" t="n">
-        <v>0.2334</v>
+        <v>0.3605</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2027</v>
+        <v>0.2894</v>
       </c>
       <c r="G119" t="n">
         <v>0.3464</v>
@@ -3025,7 +3025,7 @@
         <v>0.3054</v>
       </c>
       <c r="F120" t="n">
-        <v>0.29</v>
+        <v>0.3177</v>
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="n">
-        <v>0.2026</v>
+        <v>0.2099</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -3058,7 +3058,7 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>0.2234</v>
+        <v>0.3771</v>
       </c>
       <c r="F122" t="n">
         <v>0.21</v>
@@ -3079,10 +3079,10 @@
         <v>0.243</v>
       </c>
       <c r="F123" t="n">
-        <v>0.2195</v>
+        <v>0.2425</v>
       </c>
       <c r="G123" t="n">
-        <v>0.2602</v>
+        <v>0.3184</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -3096,13 +3096,13 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.2121</v>
+        <v>0.4925</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2083</v>
+        <v>0.4068</v>
       </c>
       <c r="G124" t="n">
-        <v>0.2158</v>
+        <v>0.4912</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>0.2099</v>
+        <v>0.2438</v>
       </c>
       <c r="D126" t="n">
         <v>0.2259</v>
@@ -3146,10 +3146,10 @@
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>0.2254</v>
+        <v>0.2868</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2185</v>
+        <v>0.2879</v>
       </c>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
         <v>0.2443</v>
       </c>
       <c r="H127" t="n">
-        <v>0.2224</v>
+        <v>0.2445</v>
       </c>
     </row>
     <row r="128">
@@ -3168,10 +3168,10 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>0.2643</v>
+        <v>0.2943</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2177</v>
+        <v>0.2482</v>
       </c>
       <c r="E128" t="n">
         <v>0.2069</v>
@@ -3253,14 +3253,14 @@
         <v>0.2766</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2165</v>
+        <v>0.2725</v>
       </c>
       <c r="E132" t="n">
         <v>0.2942</v>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="n">
-        <v>0.2305</v>
+        <v>0.2693</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3317,7 +3317,7 @@
         <v>0.2048</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2038</v>
+        <v>0.2963</v>
       </c>
     </row>
     <row r="136">
@@ -3356,7 +3356,7 @@
         <v>0.2007</v>
       </c>
       <c r="G137" t="n">
-        <v>0.2431</v>
+        <v>0.307</v>
       </c>
       <c r="H137" t="n">
         <v>0.2321</v>
@@ -3369,22 +3369,22 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.2384</v>
+        <v>0.3908</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2697</v>
+        <v>0.3421</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2278</v>
+        <v>0.4671</v>
       </c>
       <c r="E138" t="n">
-        <v>0.3119</v>
+        <v>0.4439</v>
       </c>
       <c r="F138" t="n">
-        <v>0.2694</v>
+        <v>0.3571</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2792</v>
+        <v>0.4066</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3395,17 +3395,17 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.2423</v>
+        <v>0.2511</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2123</v>
+        <v>0.2187</v>
       </c>
       <c r="D139" t="n">
-        <v>0.245</v>
+        <v>0.2957</v>
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="n">
-        <v>0.2665</v>
+        <v>0.3622</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="n">
-        <v>0.3437</v>
+        <v>0.3529</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="n">
-        <v>0.234</v>
+        <v>0.4113</v>
       </c>
       <c r="E141" t="n">
         <v>0.2166</v>
@@ -3444,7 +3444,7 @@
         <v>0.4439</v>
       </c>
       <c r="G141" t="n">
-        <v>0.211</v>
+        <v>0.4741</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -3455,22 +3455,22 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.3371</v>
+        <v>0.3947</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2977</v>
+        <v>0.5619</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2379</v>
+        <v>0.532</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2725</v>
+        <v>0.3157</v>
       </c>
       <c r="F142" t="n">
-        <v>0.21</v>
+        <v>0.2317</v>
       </c>
       <c r="G142" t="n">
-        <v>0.2262</v>
+        <v>0.5889</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3484,16 +3484,16 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0.2149</v>
+        <v>0.4226</v>
       </c>
       <c r="F143" t="n">
         <v>0.3944</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2092</v>
+        <v>0.5129</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2885</v>
+        <v>0.4625</v>
       </c>
     </row>
     <row r="144">
@@ -3526,13 +3526,13 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>0.2467</v>
+        <v>0.269</v>
       </c>
       <c r="F145" t="n">
         <v>0.238</v>
       </c>
       <c r="G145" t="n">
-        <v>0.2346</v>
+        <v>0.2744</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -3546,13 +3546,13 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>0.2067</v>
+        <v>0.2237</v>
       </c>
       <c r="F146" t="n">
         <v>0.2104</v>
       </c>
       <c r="G146" t="n">
-        <v>0.2022</v>
+        <v>0.2338</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -3568,7 +3568,7 @@
         <v>0.2439</v>
       </c>
       <c r="E147" t="n">
-        <v>0.2077</v>
+        <v>0.2649</v>
       </c>
       <c r="F147" t="n">
         <v>0.2287</v>
